--- a/rtos-api-analysis/results/rt-thread_runtime_info.xlsx
+++ b/rtos-api-analysis/results/rt-thread_runtime_info.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -517,31 +517,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>273</v>
+        <v>42</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -557,31 +557,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>730</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>915</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -637,31 +637,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -676,36 +676,37 @@
           <t>sys_getaddrinfo</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B7" t="n">
+        <v>89</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3805</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/net/sal/src/sal_socket.c:1575
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -716,31 +717,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20225</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>607024</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -756,31 +757,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1104</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -796,21 +797,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -820,7 +821,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -836,21 +837,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -860,7 +861,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -876,21 +877,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>199</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -900,7 +901,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -915,36 +916,37 @@
           <t>sys_ioctl</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/dfs/dfs_v2/src/dfs_file.c:1172
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -955,21 +957,21 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -979,7 +981,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -995,21 +997,21 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>877</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1019,7 +1021,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1035,21 +1037,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1059,7 +1061,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1075,21 +1077,21 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>564</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1099,7 +1101,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1115,7 +1117,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1124,7 +1126,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1155,7 +1157,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1164,7 +1166,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>758</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1195,16 +1197,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1214,7 +1216,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1235,31 +1237,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1275,7 +1277,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1284,7 +1286,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>691</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1315,21 +1317,21 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1339,7 +1341,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1354,36 +1356,37 @@
           <t>sys_fsync</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/dfs/dfs_v2/src/dfs_file.c:1273
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1394,31 +1397,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>378</v>
+        <v>111</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1434,7 +1437,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1443,7 +1446,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1474,31 +1477,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1514,21 +1517,21 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>636</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>27385</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1538,7 +1541,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1554,31 +1557,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>705</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1594,7 +1597,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1603,22 +1606,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>202</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1633,36 +1636,37 @@
           <t>sys_closesocket</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/net/sal/src/sal_socket.c:1127
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1677,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1682,7 +1686,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1713,31 +1717,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>730</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1753,16 +1757,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1772,7 +1776,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1792,36 +1796,37 @@
           <t>sys_mutex_take</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B35" t="n">
+        <v>686</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>35883</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>322</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: src/scheduler_up.c:537
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1832,21 +1837,21 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>233</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1856,7 +1861,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1872,16 +1877,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>687</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1891,7 +1896,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1912,31 +1917,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5948</v>
+        <v>105</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>129488</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1952,31 +1957,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1992,31 +1997,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1925</v>
+        <v>233</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>46123</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2032,31 +2037,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>24396</v>
+        <v>27</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>610177</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2099,7 +2104,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:261
+          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:271
 </t>
         </is>
       </c>
@@ -2110,36 +2115,37 @@
           <t>sys_ftruncate</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B43" t="n">
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/dfs/dfs_v2/src/dfs_file.c:1744
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2156,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2190,7 +2196,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2199,7 +2205,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>690</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2230,21 +2236,21 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2254,7 +2260,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2270,31 +2276,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2310,7 +2316,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2319,7 +2325,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>320</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2350,21 +2356,21 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2374,7 +2380,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2389,36 +2395,37 @@
           <t>sys_fstat</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B50" t="n">
+        <v>5</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/dfs/dfs_v2/src/dfs_posix.c:576
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2428,37 +2435,36 @@
           <t>sys_clock_settime</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>27</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:271
+</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2475,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2509,31 +2515,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2549,31 +2555,31 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2023</v>
+        <v>33</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>34907</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2589,16 +2595,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2608,7 +2614,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2629,31 +2635,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2669,7 +2675,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2678,7 +2684,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2709,31 +2715,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2749,31 +2755,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3028</v>
+        <v>387</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>104400</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>160</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2789,31 +2795,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1323</v>
+        <v>8</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>51835</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2828,36 +2834,37 @@
           <t>sys_epoll_ctl</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B61" t="n">
+        <v>18</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/dfs/dfs_v2/src/dfs.c:315
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2884,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2908,31 +2915,31 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2948,31 +2955,31 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>203</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2987,36 +2994,37 @@
           <t>sys_select</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B65" t="n">
+        <v>9280</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>2193</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>542668</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: src/klibc/rt_vsnprintf_tiny.c:334
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3027,31 +3035,31 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4090</v>
+        <v>351</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>104400</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>160</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3066,36 +3074,37 @@
           <t>sys_shmrm</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B67" t="n">
+        <v>15</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/mm/mm_page.c:339
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3106,31 +3115,31 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>566</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3146,16 +3155,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3165,7 +3174,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3186,31 +3195,31 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3226,31 +3235,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2098</v>
+        <v>92</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>82780</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3293,7 +3302,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:311
+          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:271
 </t>
         </is>
       </c>
@@ -3305,7 +3314,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3314,7 +3323,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3345,21 +3354,21 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3369,7 +3378,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3385,7 +3394,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3394,7 +3403,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3425,7 +3434,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3434,22 +3443,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3465,16 +3474,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3484,7 +3493,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3505,7 +3514,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3545,7 +3554,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3554,7 +3563,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>782</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3585,31 +3594,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3096</v>
+        <v>366</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>104400</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>160</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3625,31 +3634,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>154</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3665,7 +3674,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3674,7 +3683,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3705,31 +3714,31 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>7263</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3745,7 +3754,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3754,7 +3763,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3769,7 +3778,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3785,31 +3794,31 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>9316</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>266320</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3825,31 +3834,31 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>18286</v>
+        <v>283</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>559289</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3892,7 +3901,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:197
+          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:198
 </t>
         </is>
       </c>
@@ -3904,7 +3913,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3913,7 +3922,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3943,36 +3952,37 @@
           <t>sys_setrlimit</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B89" t="n">
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/lwp/test_files/sys_setrlimit.c:104
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4020,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:355
+          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:362
 </t>
         </is>
       </c>
@@ -4021,36 +4031,37 @@
           <t>sys_getpeername</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B91" t="n">
+        <v>2</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/net/sal/src/sal_socket.c:773
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4061,31 +4072,31 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4110,7 +4121,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4141,31 +4152,31 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>693</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4181,31 +4192,31 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>18610</v>
+        <v>159</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>335243</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4221,31 +4232,31 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>31</v>
+        <v>275</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>113</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>13510</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4261,31 +4272,31 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1408</v>
+        <v>8</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>51835</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4300,36 +4311,37 @@
           <t>sys_event_recv</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B98" t="n">
+        <v>1076</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>51797</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>295</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: src/cpu_up.c:63
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4339,36 +4351,37 @@
           <t>sys_bind</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B99" t="n">
+        <v>2</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/net/sal/src/sal_socket.c:724
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4379,16 +4392,16 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4398,7 +4411,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4419,16 +4432,16 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>720</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4438,7 +4451,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4459,7 +4472,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4468,7 +4481,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4499,21 +4512,21 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4523,7 +4536,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4538,36 +4551,37 @@
           <t>sys_getsockname</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B104" t="n">
+        <v>2</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/net/sal/src/sal_socket.c:787
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4619,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:428
+          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:432
 </t>
         </is>
       </c>
@@ -4617,16 +4631,16 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4636,7 +4650,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4684,7 +4698,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:311
+          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:271
 </t>
         </is>
       </c>
@@ -4696,16 +4710,16 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4715,7 +4729,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4736,21 +4750,21 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4760,7 +4774,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4776,7 +4790,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -4816,31 +4830,31 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>743</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4856,31 +4870,31 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>848</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4895,36 +4909,37 @@
           <t>sys_fstatfs64</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B113" t="n">
+        <v>3</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/dfs/dfs_v2/src/dfs_posix.c:797
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4950,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -4944,7 +4959,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4975,7 +4990,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -4984,7 +4999,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5015,31 +5030,31 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>12730</v>
+        <v>2929</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>432085</t>
+          <t>147532</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>312</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5055,21 +5070,21 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5079,7 +5094,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5095,16 +5110,16 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5114,7 +5129,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5162,7 +5177,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:398
+          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:405
 </t>
         </is>
       </c>
@@ -5174,31 +5189,31 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>966</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5223,7 +5238,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5254,21 +5269,21 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5278,7 +5293,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5294,31 +5309,31 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>1091</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5334,31 +5349,31 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>155</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5374,7 +5389,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -5383,7 +5398,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>815</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5414,31 +5429,31 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>7546</v>
+        <v>51</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>144442</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5454,31 +5469,31 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>19807</v>
+        <v>3421</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>659115</t>
+          <t>178767</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>744</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5494,16 +5509,16 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5513,7 +5528,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5534,31 +5549,31 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>895</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5574,16 +5589,16 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5593,7 +5608,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5614,7 +5629,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -5623,7 +5638,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>829</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5654,21 +5669,21 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>928</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5678,7 +5693,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5693,36 +5708,37 @@
           <t>sys_lseek</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B133" t="n">
+        <v>1</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/dfs/dfs_v2/src/dfs_file.c:966
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5733,31 +5749,31 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5773,31 +5789,31 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>888</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5812,36 +5828,37 @@
           <t>sys_prlimit64</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B136" t="n">
+        <v>1</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/lwp/test_files/sys_prlimit64.c:110
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5852,31 +5869,31 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>153</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5892,31 +5909,31 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5932,31 +5949,31 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>152</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5972,31 +5989,31 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>730</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6012,31 +6029,31 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6052,31 +6069,31 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>818</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6091,36 +6108,37 @@
           <t>sys_rt_timer_control</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B143" t="n">
+        <v>22</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: src/timer.c:722
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6158,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6198,7 +6216,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:311
+          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:315
 </t>
         </is>
       </c>
@@ -6210,31 +6228,31 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6250,31 +6268,31 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>697</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6290,7 +6308,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -6299,7 +6317,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -6330,21 +6348,21 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6354,7 +6372,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6370,21 +6388,21 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6394,7 +6412,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6409,36 +6427,37 @@
           <t>sys_accept</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B151" t="n">
+        <v>4</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/net/sal/src/sal_socket.c:616
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6468,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -6458,7 +6477,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>774</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6489,7 +6508,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -6498,7 +6517,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6529,7 +6548,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -6538,22 +6557,22 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6569,31 +6588,31 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>188</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6609,21 +6628,21 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6649,31 +6668,31 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6689,31 +6708,31 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2974</v>
+        <v>1</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>92523</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6756,7 +6775,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/lwp/lwp_runtime.c:151
+          <t xml:space="preserve">KLEE: Execute: src/ipc.c:0
 </t>
         </is>
       </c>
@@ -6768,31 +6787,31 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6808,31 +6827,31 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>562</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6848,31 +6867,31 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6887,36 +6906,37 @@
           <t>sys_exit_group</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B163" t="n">
+        <v>2512</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>107976</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>485</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>885</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: src/object.c:574
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -6927,21 +6947,21 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>710</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6951,7 +6971,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6967,31 +6987,31 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>3271</v>
+        <v>402</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>104400</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>160</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7007,31 +7027,31 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7047,7 +7067,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -7056,7 +7076,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7071,7 +7091,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7087,7 +7107,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -7096,7 +7116,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -7127,7 +7147,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -7136,7 +7156,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -7167,7 +7187,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -7176,7 +7196,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -7207,7 +7227,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -7216,7 +7236,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>758</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -7247,7 +7267,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -7256,7 +7276,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>557</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -7286,37 +7306,36 @@
           <t>sys_thread_create</t>
         </is>
       </c>
-      <c r="B173" t="n">
-        <v>3</v>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t xml:space="preserve">KLEE: Execute: components/lwp/lwp_ipc.c:486
+</t>
         </is>
       </c>
     </row>
@@ -7327,31 +7346,31 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7367,21 +7386,21 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7391,7 +7410,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7407,31 +7426,31 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>634</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7446,36 +7465,37 @@
           <t>sys_listen</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B177" t="n">
+        <v>1</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/net/sal/src/sal_socket.c:892
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -7486,31 +7506,31 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -7526,31 +7546,31 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -7566,16 +7586,16 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>633</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7585,7 +7605,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7606,7 +7626,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -7615,7 +7635,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -7646,21 +7666,21 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7670,7 +7690,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -7685,36 +7705,37 @@
           <t>sys_connect</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B183" t="n">
+        <v>3</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/net/sal/src/sal_socket.c:865
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -7725,16 +7746,16 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7744,7 +7765,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7765,31 +7786,31 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -7805,21 +7826,21 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -7829,7 +7850,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -7845,21 +7866,21 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -7869,7 +7890,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -7885,31 +7906,31 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -7924,36 +7945,37 @@
           <t>sys_shmat</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B189" t="n">
+        <v>14</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/mm/mm_aspace.c:604
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -7964,31 +7986,31 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>3188</v>
+        <v>387</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>104400</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>160</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8004,31 +8026,31 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>449</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8044,7 +8066,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -8053,7 +8075,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -8084,7 +8106,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -8093,7 +8115,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -8124,31 +8146,31 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>154</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -8164,21 +8186,21 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>113</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8188,7 +8210,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -8204,21 +8226,21 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8228,7 +8250,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -8243,36 +8265,37 @@
           <t>sys_fstatfs</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B197" t="n">
+        <v>3</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/dfs/dfs_v2/src/dfs_posix.c:797
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -8283,16 +8306,16 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -8302,7 +8325,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -8323,7 +8346,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -8332,7 +8355,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -8363,31 +8386,31 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>3332</v>
+        <v>410</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>104400</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>160</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -8403,31 +8426,31 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>24</v>
+        <v>513</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>266</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>26978</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -8443,7 +8466,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -8452,7 +8475,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -8483,31 +8506,31 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>914</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -8523,31 +8546,31 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -8562,37 +8585,36 @@
           <t>sys_clock_gettime</t>
         </is>
       </c>
-      <c r="B205" t="n">
-        <v>29</v>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:271
+</t>
         </is>
       </c>
     </row>
@@ -8602,36 +8624,37 @@
           <t>sys_shutdown</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B206" t="n">
+        <v>1</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/net/sal/src/sal_socket.c:740
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8665,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.8292682926829268</v>
+        <v>0.9414634146341463</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>

--- a/rtos-api-analysis/results/rt-thread_runtime_info.xlsx
+++ b/rtos-api-analysis/results/rt-thread_runtime_info.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1797,21 +1797,21 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>397</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>35919</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>323</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2076,36 +2076,37 @@
           <t>sys_device_open</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B42" t="n">
+        <v>45</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2636</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:271
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2117,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2276,7 +2277,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2316,7 +2317,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2356,7 +2357,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2396,7 +2397,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2435,36 +2436,37 @@
           <t>sys_clock_settime</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B51" t="n">
+        <v>106</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4162</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:271
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2517,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2555,7 +2557,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2635,7 +2637,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2675,7 +2677,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2715,7 +2717,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2755,7 +2757,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2875,7 +2877,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2915,7 +2917,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2955,7 +2957,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2995,31 +2997,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>9280</v>
+        <v>9345</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>542668</t>
+          <t>540138</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3035,7 +3037,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3075,7 +3077,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3115,7 +3117,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3155,7 +3157,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3235,7 +3237,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3274,36 +3276,37 @@
           <t>sys_getrandom</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B72" t="n">
+        <v>248</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>12182</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:271
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3317,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3474,7 +3477,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3554,7 +3557,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3594,7 +3597,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3634,7 +3637,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -3794,7 +3797,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3834,7 +3837,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3873,36 +3876,37 @@
           <t>sys_device_init</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B87" t="n">
+        <v>6</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:198
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3917,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3953,7 +3957,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -3992,36 +3996,37 @@
           <t>sys_device_read</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B90" t="n">
+        <v>15</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:362
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4037,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4072,7 +4077,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4112,7 +4117,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4152,7 +4157,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4192,7 +4197,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4232,7 +4237,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4272,7 +4277,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4312,7 +4317,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1076</v>
+        <v>1058</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -4352,7 +4357,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4392,7 +4397,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4432,7 +4437,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4512,7 +4517,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4591,36 +4596,37 @@
           <t>sys_device_control</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B105" t="n">
+        <v>13</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:432
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4670,36 +4676,37 @@
           <t>sys_clock_getres</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B107" t="n">
+        <v>99</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>4580</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:271
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4717,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -4830,7 +4837,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -4870,7 +4877,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -4910,7 +4917,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -4950,7 +4957,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -4990,7 +4997,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5030,31 +5037,31 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2929</v>
+        <v>2850</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>147532</t>
+          <t>141180</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>298</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5110,7 +5117,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5149,36 +5156,37 @@
           <t>sys_device_write</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B119" t="n">
+        <v>14</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:405
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5197,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -5229,7 +5237,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -5269,7 +5277,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -5309,7 +5317,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -5389,7 +5397,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -5429,7 +5437,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -5469,31 +5477,31 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3421</v>
+        <v>2952</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>178767</t>
+          <t>145382</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>604</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5509,7 +5517,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -5549,7 +5557,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -5589,7 +5597,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -5629,7 +5637,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -5669,7 +5677,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -5709,7 +5717,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -5749,7 +5757,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -5789,7 +5797,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -5869,7 +5877,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -5909,7 +5917,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -5949,7 +5957,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6029,7 +6037,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -6069,7 +6077,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -6109,7 +6117,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -6188,36 +6196,37 @@
           <t>sys_device_close</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B145" t="n">
+        <v>8</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:315
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6277,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -6348,7 +6357,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -6428,7 +6437,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -6468,7 +6477,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -6508,7 +6517,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -6548,7 +6557,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -6588,7 +6597,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -6668,7 +6677,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -6775,7 +6784,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: src/ipc.c:0
+          <t xml:space="preserve">KLEE: Execute: src/ipc.c:854
 </t>
         </is>
       </c>
@@ -6827,7 +6836,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -6867,7 +6876,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -6907,31 +6916,31 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2512</v>
+        <v>2431</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>107976</t>
+          <t>100260</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>455</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>815</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6947,7 +6956,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -6987,7 +6996,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -7027,7 +7036,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -7107,7 +7116,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -7147,7 +7156,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -7187,7 +7196,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -7227,7 +7236,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -7267,7 +7276,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -7306,36 +7315,37 @@
           <t>sys_thread_create</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B173" t="n">
+        <v>4140</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>181265</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>266</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/lwp/lwp_ipc.c:486
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7356,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -7386,7 +7396,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -7506,7 +7516,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -7546,7 +7556,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -7586,7 +7596,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -7626,7 +7636,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -7666,7 +7676,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -7706,7 +7716,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -7746,7 +7756,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -7786,7 +7796,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -7826,7 +7836,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -7906,7 +7916,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -7986,7 +7996,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -8106,7 +8116,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -8146,7 +8156,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -8186,7 +8196,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -8266,7 +8276,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -8306,7 +8316,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -8346,7 +8356,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -8386,7 +8396,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -8426,7 +8436,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>513</v>
+        <v>492</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -8506,7 +8516,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -8546,7 +8556,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -8585,36 +8595,37 @@
           <t>sys_clock_gettime</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B205" t="n">
+        <v>116</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>4766</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: components/drivers/core/device.c:271
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8676,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.9414634146341463</v>
+        <v>0.9951219512195122</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
